--- a/artfynd/A 44368-2026 artfynd.xlsx
+++ b/artfynd/A 44368-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44368-2026 artfynd.xlsx
+++ b/artfynd/A 44368-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
